--- a/final_data_pipeline/output/325311_elec_options.xlsx
+++ b/final_data_pipeline/output/325311_elec_options.xlsx
@@ -1041,7 +1041,7 @@
         <v>154</v>
       </c>
       <c r="AD2">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AE2">
         <v>8000</v>
@@ -1136,7 +1136,7 @@
         <v>155</v>
       </c>
       <c r="AD3">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AE3">
         <v>8000</v>
@@ -1231,7 +1231,7 @@
         <v>154</v>
       </c>
       <c r="AD4">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AE4">
         <v>8000</v>
@@ -1326,7 +1326,7 @@
         <v>154</v>
       </c>
       <c r="AD5">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AE5">
         <v>8000</v>
@@ -1421,7 +1421,7 @@
         <v>155</v>
       </c>
       <c r="AD6">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AE6">
         <v>8000</v>
@@ -1516,7 +1516,7 @@
         <v>155</v>
       </c>
       <c r="AD7">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AE7">
         <v>8000</v>
@@ -1611,7 +1611,7 @@
         <v>154</v>
       </c>
       <c r="AD8">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE8">
         <v>8000</v>
@@ -1706,7 +1706,7 @@
         <v>155</v>
       </c>
       <c r="AD9">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE9">
         <v>8000</v>
@@ -1801,7 +1801,7 @@
         <v>154</v>
       </c>
       <c r="AD10">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE10">
         <v>8000</v>
@@ -1896,7 +1896,7 @@
         <v>154</v>
       </c>
       <c r="AD11">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE11">
         <v>8000</v>
@@ -1991,7 +1991,7 @@
         <v>155</v>
       </c>
       <c r="AD12">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE12">
         <v>8000</v>
@@ -2086,7 +2086,7 @@
         <v>155</v>
       </c>
       <c r="AD13">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE13">
         <v>8000</v>
@@ -3891,7 +3891,7 @@
         <v>154</v>
       </c>
       <c r="AD32">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AE32">
         <v>8000</v>
@@ -3986,7 +3986,7 @@
         <v>154</v>
       </c>
       <c r="AD33">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AE33">
         <v>8000</v>
@@ -4081,7 +4081,7 @@
         <v>154</v>
       </c>
       <c r="AD34">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AE34">
         <v>8000</v>
@@ -4176,7 +4176,7 @@
         <v>155</v>
       </c>
       <c r="AD35">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AE35">
         <v>8000</v>
@@ -4271,7 +4271,7 @@
         <v>155</v>
       </c>
       <c r="AD36">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AE36">
         <v>8000</v>
@@ -4366,7 +4366,7 @@
         <v>155</v>
       </c>
       <c r="AD37">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AE37">
         <v>8000</v>
@@ -14151,7 +14151,7 @@
         <v>155</v>
       </c>
       <c r="AD140">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE140">
         <v>8000</v>
@@ -14246,7 +14246,7 @@
         <v>155</v>
       </c>
       <c r="AD141">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE141">
         <v>8000</v>
@@ -14341,7 +14341,7 @@
         <v>154</v>
       </c>
       <c r="AD142">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE142">
         <v>8000</v>
@@ -14436,7 +14436,7 @@
         <v>155</v>
       </c>
       <c r="AD143">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE143">
         <v>8000</v>
@@ -14531,7 +14531,7 @@
         <v>154</v>
       </c>
       <c r="AD144">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE144">
         <v>8000</v>
@@ -14626,7 +14626,7 @@
         <v>155</v>
       </c>
       <c r="AD145">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE145">
         <v>8000</v>
@@ -14721,7 +14721,7 @@
         <v>154</v>
       </c>
       <c r="AD146">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE146">
         <v>8000</v>
@@ -14816,7 +14816,7 @@
         <v>155</v>
       </c>
       <c r="AD147">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE147">
         <v>8000</v>
@@ -14911,7 +14911,7 @@
         <v>154</v>
       </c>
       <c r="AD148">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE148">
         <v>8000</v>
@@ -15006,7 +15006,7 @@
         <v>154</v>
       </c>
       <c r="AD149">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE149">
         <v>8000</v>
@@ -15101,7 +15101,7 @@
         <v>154</v>
       </c>
       <c r="AD150">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE150">
         <v>8000</v>
@@ -15196,7 +15196,7 @@
         <v>155</v>
       </c>
       <c r="AD151">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE151">
         <v>8000</v>
@@ -18141,7 +18141,7 @@
         <v>154</v>
       </c>
       <c r="AD182">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AE182">
         <v>8000</v>
@@ -18239,7 +18239,7 @@
         <v>154</v>
       </c>
       <c r="AD183">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AE183">
         <v>8000</v>
@@ -18334,7 +18334,7 @@
         <v>154</v>
       </c>
       <c r="AD184">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AE184">
         <v>8000</v>
@@ -18429,7 +18429,7 @@
         <v>155</v>
       </c>
       <c r="AD185">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AE185">
         <v>8000</v>
@@ -18524,7 +18524,7 @@
         <v>154</v>
       </c>
       <c r="AD186">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AE186">
         <v>8000</v>
@@ -18619,7 +18619,7 @@
         <v>155</v>
       </c>
       <c r="AD187">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AE187">
         <v>8000</v>
@@ -18714,7 +18714,7 @@
         <v>155</v>
       </c>
       <c r="AD188">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AE188">
         <v>8000</v>
@@ -18809,7 +18809,7 @@
         <v>155</v>
       </c>
       <c r="AD189">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AE189">
         <v>8000</v>
@@ -18904,7 +18904,7 @@
         <v>154</v>
       </c>
       <c r="AD190">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AE190">
         <v>8000</v>
@@ -18999,7 +18999,7 @@
         <v>154</v>
       </c>
       <c r="AD191">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AE191">
         <v>8000</v>
@@ -19094,7 +19094,7 @@
         <v>154</v>
       </c>
       <c r="AD192">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AE192">
         <v>8000</v>
@@ -19189,7 +19189,7 @@
         <v>155</v>
       </c>
       <c r="AD193">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AE193">
         <v>8000</v>
@@ -19284,7 +19284,7 @@
         <v>155</v>
       </c>
       <c r="AD194">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AE194">
         <v>8000</v>
@@ -20519,7 +20519,7 @@
         <v>154</v>
       </c>
       <c r="AD207">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE207">
         <v>8000</v>
@@ -20614,7 +20614,7 @@
         <v>154</v>
       </c>
       <c r="AD208">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE208">
         <v>8000</v>
@@ -20712,7 +20712,7 @@
         <v>154</v>
       </c>
       <c r="AD209">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE209">
         <v>8000</v>
@@ -20807,7 +20807,7 @@
         <v>154</v>
       </c>
       <c r="AD210">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE210">
         <v>8000</v>
@@ -20902,7 +20902,7 @@
         <v>155</v>
       </c>
       <c r="AD211">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE211">
         <v>8000</v>
@@ -20997,7 +20997,7 @@
         <v>155</v>
       </c>
       <c r="AD212">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE212">
         <v>8000</v>
@@ -21092,7 +21092,7 @@
         <v>155</v>
       </c>
       <c r="AD213">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE213">
         <v>8000</v>
@@ -21757,7 +21757,7 @@
         <v>155</v>
       </c>
       <c r="AD220">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AE220">
         <v>8000</v>
@@ -21852,7 +21852,7 @@
         <v>155</v>
       </c>
       <c r="AD221">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AE221">
         <v>8000</v>
@@ -21947,7 +21947,7 @@
         <v>154</v>
       </c>
       <c r="AD222">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AE222">
         <v>8000</v>
@@ -22042,7 +22042,7 @@
         <v>154</v>
       </c>
       <c r="AD223">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AE223">
         <v>8000</v>
@@ -22137,7 +22137,7 @@
         <v>155</v>
       </c>
       <c r="AD224">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AE224">
         <v>8000</v>
@@ -22232,7 +22232,7 @@
         <v>154</v>
       </c>
       <c r="AD225">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AE225">
         <v>8000</v>
@@ -23467,7 +23467,7 @@
         <v>155</v>
       </c>
       <c r="AD238">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE238">
         <v>8000</v>
@@ -23562,7 +23562,7 @@
         <v>155</v>
       </c>
       <c r="AD239">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE239">
         <v>8000</v>
@@ -23657,7 +23657,7 @@
         <v>155</v>
       </c>
       <c r="AD240">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE240">
         <v>8000</v>
@@ -23752,7 +23752,7 @@
         <v>155</v>
       </c>
       <c r="AD241">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE241">
         <v>8000</v>
@@ -23847,7 +23847,7 @@
         <v>155</v>
       </c>
       <c r="AD242">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE242">
         <v>8000</v>
@@ -23942,7 +23942,7 @@
         <v>155</v>
       </c>
       <c r="AD243">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE243">
         <v>8000</v>
@@ -24037,7 +24037,7 @@
         <v>155</v>
       </c>
       <c r="AD244">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE244">
         <v>8000</v>
@@ -24132,7 +24132,7 @@
         <v>155</v>
       </c>
       <c r="AD245">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE245">
         <v>8000</v>
@@ -24227,7 +24227,7 @@
         <v>155</v>
       </c>
       <c r="AD246">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE246">
         <v>8000</v>
@@ -24322,7 +24322,7 @@
         <v>154</v>
       </c>
       <c r="AD247">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE247">
         <v>8000</v>
@@ -24417,7 +24417,7 @@
         <v>154</v>
       </c>
       <c r="AD248">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE248">
         <v>8000</v>
@@ -24512,7 +24512,7 @@
         <v>154</v>
       </c>
       <c r="AD249">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE249">
         <v>8000</v>
@@ -24607,7 +24607,7 @@
         <v>154</v>
       </c>
       <c r="AD250">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE250">
         <v>8000</v>
@@ -24702,7 +24702,7 @@
         <v>154</v>
       </c>
       <c r="AD251">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE251">
         <v>8000</v>
@@ -24797,7 +24797,7 @@
         <v>155</v>
       </c>
       <c r="AD252">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE252">
         <v>8000</v>
@@ -24892,7 +24892,7 @@
         <v>155</v>
       </c>
       <c r="AD253">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE253">
         <v>8000</v>
@@ -24987,7 +24987,7 @@
         <v>154</v>
       </c>
       <c r="AD254">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE254">
         <v>8000</v>
@@ -25082,7 +25082,7 @@
         <v>155</v>
       </c>
       <c r="AD255">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE255">
         <v>8000</v>
@@ -25177,7 +25177,7 @@
         <v>154</v>
       </c>
       <c r="AD256">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE256">
         <v>8000</v>
@@ -25272,7 +25272,7 @@
         <v>154</v>
       </c>
       <c r="AD257">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE257">
         <v>8000</v>
@@ -25367,7 +25367,7 @@
         <v>155</v>
       </c>
       <c r="AD258">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE258">
         <v>8000</v>
@@ -25462,7 +25462,7 @@
         <v>154</v>
       </c>
       <c r="AD259">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE259">
         <v>8000</v>
@@ -25557,7 +25557,7 @@
         <v>154</v>
       </c>
       <c r="AD260">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE260">
         <v>8000</v>
@@ -25652,7 +25652,7 @@
         <v>155</v>
       </c>
       <c r="AD261">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE261">
         <v>8000</v>
@@ -25747,7 +25747,7 @@
         <v>154</v>
       </c>
       <c r="AD262">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE262">
         <v>8000</v>
@@ -25842,7 +25842,7 @@
         <v>154</v>
       </c>
       <c r="AD263">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE263">
         <v>8000</v>
@@ -25937,7 +25937,7 @@
         <v>154</v>
       </c>
       <c r="AD264">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE264">
         <v>8000</v>
@@ -26032,7 +26032,7 @@
         <v>154</v>
       </c>
       <c r="AD265">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE265">
         <v>8000</v>
@@ -26127,7 +26127,7 @@
         <v>154</v>
       </c>
       <c r="AD266">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE266">
         <v>8000</v>
@@ -26222,7 +26222,7 @@
         <v>154</v>
       </c>
       <c r="AD267">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE267">
         <v>8000</v>
@@ -26317,7 +26317,7 @@
         <v>154</v>
       </c>
       <c r="AD268">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE268">
         <v>8000</v>
@@ -26412,7 +26412,7 @@
         <v>155</v>
       </c>
       <c r="AD269">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE269">
         <v>8000</v>
@@ -26507,7 +26507,7 @@
         <v>155</v>
       </c>
       <c r="AD270">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE270">
         <v>8000</v>
@@ -26602,7 +26602,7 @@
         <v>155</v>
       </c>
       <c r="AD271">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE271">
         <v>8000</v>
@@ -26697,7 +26697,7 @@
         <v>154</v>
       </c>
       <c r="AD272">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE272">
         <v>8000</v>
@@ -26792,7 +26792,7 @@
         <v>155</v>
       </c>
       <c r="AD273">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE273">
         <v>8000</v>
@@ -27457,7 +27457,7 @@
         <v>154</v>
       </c>
       <c r="AD280">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="AE280">
         <v>8000</v>
@@ -27552,7 +27552,7 @@
         <v>155</v>
       </c>
       <c r="AD281">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="AE281">
         <v>8000</v>
@@ -27647,7 +27647,7 @@
         <v>154</v>
       </c>
       <c r="AD282">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="AE282">
         <v>8000</v>
@@ -27742,7 +27742,7 @@
         <v>154</v>
       </c>
       <c r="AD283">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="AE283">
         <v>8000</v>
@@ -27837,7 +27837,7 @@
         <v>155</v>
       </c>
       <c r="AD284">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="AE284">
         <v>8000</v>
@@ -27932,7 +27932,7 @@
         <v>155</v>
       </c>
       <c r="AD285">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="AE285">
         <v>8000</v>
@@ -29167,7 +29167,7 @@
         <v>154</v>
       </c>
       <c r="AD298">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE298">
         <v>8000</v>
@@ -29262,7 +29262,7 @@
         <v>154</v>
       </c>
       <c r="AD299">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE299">
         <v>8000</v>
@@ -29357,7 +29357,7 @@
         <v>155</v>
       </c>
       <c r="AD300">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE300">
         <v>8000</v>
@@ -29452,7 +29452,7 @@
         <v>155</v>
       </c>
       <c r="AD301">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE301">
         <v>8000</v>
@@ -29547,7 +29547,7 @@
         <v>154</v>
       </c>
       <c r="AD302">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE302">
         <v>8000</v>
@@ -29642,7 +29642,7 @@
         <v>155</v>
       </c>
       <c r="AD303">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE303">
         <v>8000</v>
@@ -32685,7 +32685,7 @@
         <v>155</v>
       </c>
       <c r="AD335">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE335">
         <v>8000</v>
@@ -32780,7 +32780,7 @@
         <v>155</v>
       </c>
       <c r="AD336">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE336">
         <v>8000</v>
@@ -32875,7 +32875,7 @@
         <v>154</v>
       </c>
       <c r="AD337">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE337">
         <v>8000</v>
@@ -32970,7 +32970,7 @@
         <v>154</v>
       </c>
       <c r="AD338">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE338">
         <v>8000</v>
@@ -33065,7 +33065,7 @@
         <v>154</v>
       </c>
       <c r="AD339">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE339">
         <v>8000</v>
@@ -33160,7 +33160,7 @@
         <v>155</v>
       </c>
       <c r="AD340">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE340">
         <v>8000</v>
@@ -33255,7 +33255,7 @@
         <v>154</v>
       </c>
       <c r="AD341">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE341">
         <v>8000</v>
@@ -33350,7 +33350,7 @@
         <v>154</v>
       </c>
       <c r="AD342">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE342">
         <v>8000</v>
@@ -33445,7 +33445,7 @@
         <v>155</v>
       </c>
       <c r="AD343">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE343">
         <v>8000</v>
@@ -33540,7 +33540,7 @@
         <v>155</v>
       </c>
       <c r="AD344">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE344">
         <v>8000</v>
@@ -33635,7 +33635,7 @@
         <v>155</v>
       </c>
       <c r="AD345">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE345">
         <v>8000</v>
@@ -33730,7 +33730,7 @@
         <v>155</v>
       </c>
       <c r="AD346">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE346">
         <v>8000</v>
@@ -33825,7 +33825,7 @@
         <v>155</v>
       </c>
       <c r="AD347">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE347">
         <v>8000</v>
@@ -33920,7 +33920,7 @@
         <v>154</v>
       </c>
       <c r="AD348">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE348">
         <v>8000</v>
@@ -34018,7 +34018,7 @@
         <v>154</v>
       </c>
       <c r="AD349">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE349">
         <v>8000</v>
@@ -34113,7 +34113,7 @@
         <v>154</v>
       </c>
       <c r="AD350">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE350">
         <v>8000</v>
@@ -34208,7 +34208,7 @@
         <v>154</v>
       </c>
       <c r="AD351">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE351">
         <v>8000</v>
@@ -34303,7 +34303,7 @@
         <v>154</v>
       </c>
       <c r="AD352">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE352">
         <v>8000</v>
@@ -34398,7 +34398,7 @@
         <v>155</v>
       </c>
       <c r="AD353">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE353">
         <v>8000</v>
